--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q10_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q10_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009512047690036489</v>
+        <v>0.009264018304975159</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009512047690036489</v>
+        <v>0.009264018304975159</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.009434790324089502</v>
+        <v>0.009159305424659888</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009434790324089502</v>
+        <v>0.009159305424659888</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.009243733737737025</v>
+        <v>0.008926553427615591</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009243733737737025</v>
+        <v>0.008926553427615591</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008943279192247175</v>
+        <v>0.008585208631063445</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008943279192247175</v>
+        <v>0.008585208631063445</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.008637601646777245</v>
+        <v>0.008248427974085709</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008637601646777245</v>
+        <v>0.008248427974085709</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0084007396500705</v>
+        <v>0.007994037726620756</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0084007396500705</v>
+        <v>0.007994037726620756</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.008262616638922792</v>
+        <v>0.0078511011088472</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008262616638922792</v>
+        <v>0.0078511011088472</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.008257107952393582</v>
+        <v>0.007851389492873324</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008257107952393582</v>
+        <v>0.007851389492873324</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -567,10 +567,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.008350904514482437</v>
+        <v>0.007960365805578039</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008350904514482437</v>
+        <v>0.007960365805578039</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -581,10 +581,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.008765777027741851</v>
+        <v>0.008391058422801644</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008765777027741851</v>
+        <v>0.008391058422801644</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -595,10 +595,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.009362936150504361</v>
+        <v>0.009006756043207059</v>
       </c>
       <c r="C12" t="n">
-        <v>0.009362936150504361</v>
+        <v>0.009006756043207059</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01022393324797814</v>
+        <v>0.009885768224714804</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01022393324797814</v>
+        <v>0.009885768224714804</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -623,10 +623,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01141570130466523</v>
+        <v>0.01109178378519962</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01141570130466523</v>
+        <v>0.01109178378519962</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -637,10 +637,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01283390977183315</v>
+        <v>0.0125204817751428</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01283390977183315</v>
+        <v>0.0125204817751428</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -651,10 +651,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01450398872347359</v>
+        <v>0.01419426373185912</v>
       </c>
       <c r="C16" t="n">
-        <v>0.01450398872347359</v>
+        <v>0.01419426373185912</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01636684303469278</v>
+        <v>0.01605157127914579</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01636684303469278</v>
+        <v>0.01605157127914579</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01835120819374153</v>
+        <v>0.01801799204753598</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01835120819374153</v>
+        <v>0.01801799204753598</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -693,10 +693,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.02046818970467592</v>
+        <v>0.02010076066918733</v>
       </c>
       <c r="C19" t="n">
-        <v>0.02046818970467592</v>
+        <v>0.02010076066918733</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -707,10 +707,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.02268550712563281</v>
+        <v>0.02226598935054477</v>
       </c>
       <c r="C20" t="n">
-        <v>0.02268550712563281</v>
+        <v>0.02226598935054477</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.02488635859325208</v>
+        <v>0.02439806090525423</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02488635859325208</v>
+        <v>0.02439806090525423</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -735,10 +735,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.02701985845247503</v>
+        <v>0.02644974001473686</v>
       </c>
       <c r="C22" t="n">
-        <v>0.02701985845247503</v>
+        <v>0.02644974001473686</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.02910904139408914</v>
+        <v>0.02844932316750634</v>
       </c>
       <c r="C23" t="n">
-        <v>0.02910904139408914</v>
+        <v>0.02844932316750634</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0313099217351753</v>
+        <v>0.03055694424519642</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0313099217351753</v>
+        <v>0.03055694424519642</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -777,10 +777,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.03373015126788502</v>
+        <v>0.03288795246213633</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03373015126788502</v>
+        <v>0.03288795246213633</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -791,10 +791,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.03647109354209699</v>
+        <v>0.03554730044385665</v>
       </c>
       <c r="C26" t="n">
-        <v>0.03647109354209699</v>
+        <v>0.03554730044385665</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.03945276816575088</v>
+        <v>0.03845754430835997</v>
       </c>
       <c r="C27" t="n">
-        <v>0.03945276816575088</v>
+        <v>0.03845754430835997</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04264538334033419</v>
+        <v>0.04159037002309293</v>
       </c>
       <c r="C28" t="n">
-        <v>0.04264538334033419</v>
+        <v>0.04159037002309293</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -833,10 +833,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.04591078146781149</v>
+        <v>0.04481258007155862</v>
       </c>
       <c r="C29" t="n">
-        <v>0.04591078146781149</v>
+        <v>0.04481258007155862</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.04911548704173103</v>
+        <v>0.04797667058535882</v>
       </c>
       <c r="C30" t="n">
-        <v>0.04911548704173103</v>
+        <v>0.04797667058535882</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -861,10 +861,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.05217472286969241</v>
+        <v>0.05100461747551364</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05217472286969241</v>
+        <v>0.05100461747551364</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
